--- a/layout/LAYOUT LID V4 LID LIQUIDACIONES.xlsx
+++ b/layout/LAYOUT LID V4 LID LIQUIDACIONES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F097C547-13B0-4DBF-BCB4-EC7F18F13AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFEDFAC-A7B9-4FF3-BB52-E45974CED576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="16440" xr2:uid="{3902425A-6075-4F3C-B792-5E3438938A95}"/>
+    <workbookView xWindow="3000" yWindow="3810" windowWidth="16960" windowHeight="10910" xr2:uid="{3902425A-6075-4F3C-B792-5E3438938A95}"/>
   </bookViews>
   <sheets>
     <sheet name="LID LIQUIDACIONES" sheetId="1" r:id="rId1"/>
@@ -206,9 +206,6 @@
     <t>ID_PAGOS_RET</t>
   </si>
   <si>
-    <t>Id_Pagos_Ret</t>
-  </si>
-  <si>
     <t>Indicador si la obligación fue realizada con atraso o no fue realizada</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>MOTIVO_RET</t>
   </si>
   <si>
-    <t>Motivo_Ret</t>
-  </si>
-  <si>
     <t>Motivo por el que la liquidación de la operación no se llevó a cabo en la hora establecida o se encuentra pendiente de liquidar de acuerdo al catalogo</t>
   </si>
   <si>
@@ -264,6 +258,12 @@
   </si>
   <si>
     <t>Fecha a la que corresponde la información</t>
+  </si>
+  <si>
+    <t>CAT_ID_PAGOS_RET</t>
+  </si>
+  <si>
+    <t>CAT_MOTIVO_RET</t>
   </si>
 </sst>
 </file>
@@ -967,22 +967,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D09A6E-0C47-4C15-88B3-2C788CD1BAEA}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="20.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.58203125" customWidth="1"/>
     <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5" customWidth="1"/>
-    <col min="8" max="8" width="9.3984375" customWidth="1"/>
-    <col min="9" max="9" width="16.19921875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" customWidth="1"/>
     <col min="11" max="11" width="21.5" customWidth="1"/>
     <col min="12" max="12" width="176" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="18.600000000000001" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>52</v>
@@ -1343,10 +1343,10 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>15</v>
@@ -1375,10 +1375,10 @@
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -1407,10 +1407,10 @@
         <v>7</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
@@ -1439,10 +1439,10 @@
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>26</v>
@@ -1468,7 +1468,7 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>52</v>
@@ -1477,10 +1477,10 @@
         <v>13</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1491,13 +1491,13 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>13</v>
@@ -1509,10 +1509,10 @@
         <v>14</v>
       </c>
       <c r="L15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>26</v>
@@ -1538,19 +1538,19 @@
         <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>15</v>
@@ -1578,7 +1578,7 @@
         <v>2</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
